--- a/filer/10360641_jem.xlsx
+++ b/filer/10360641_jem.xlsx
@@ -615,7 +615,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.)</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision</t>
         </is>
       </c>
     </row>

--- a/filer/10360641_jem.xlsx
+++ b/filer/10360641_jem.xlsx
@@ -10,7 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overblik_10360641" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="res_raw_10360641" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="balance_raw_10360641" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pengestrom_raw_10360641" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Simpel_arts" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Noter_info" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,6 +72,17 @@
       <i val="1"/>
       <color rgb="00595959"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00444444"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="8">
@@ -170,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -192,9 +205,9 @@
     <xf numFmtId="164" fontId="3" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -230,6 +243,27 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -595,7 +629,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L95"/>
+  <dimension ref="A1:L102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -615,7 +649,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Revision</t>
+          <t>Regnskabsanalyse – Resultatopgørelse &amp; Balance (t.kr.) · Klasse C-stor · Den uafhængige revisors erklær</t>
         </is>
       </c>
     </row>
@@ -629,7 +663,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Indekstal (2020=100)</t>
+          <t>Indekstal (2021=100)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -644,35 +678,35 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="4" ht="16" customHeight="1">
@@ -1498,35 +1532,35 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G22" t="inlineStr"/>
       <c r="H22" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="23" ht="16" customHeight="1">
@@ -2784,35 +2818,35 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C50" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E50" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F50" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="K50" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="51" ht="16" customHeight="1">
@@ -4166,19 +4200,19 @@
         </is>
       </c>
       <c r="B80" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C80" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F80" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="81" ht="16" customHeight="1">
@@ -4284,19 +4318,19 @@
         </is>
       </c>
       <c r="B84" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C84" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D84" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F84" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="85" ht="16" customHeight="1">
@@ -4593,6 +4627,148 @@
       </c>
       <c r="F95" s="13">
         <f>IFERROR($F$32/($F$57+$F$64)*100,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="15" t="inlineStr">
+        <is>
+          <t>PENGESTRØMSOPGØRELSE t.kr.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B98" s="17">
+        <f>'pengestrom_raw_10360641'!$B$2</f>
+        <v/>
+      </c>
+      <c r="C98" s="17">
+        <f>'pengestrom_raw_10360641'!$C$2</f>
+        <v/>
+      </c>
+      <c r="D98" s="17">
+        <f>'pengestrom_raw_10360641'!$D$2</f>
+        <v/>
+      </c>
+      <c r="E98" s="17">
+        <f>'pengestrom_raw_10360641'!$E$2</f>
+        <v/>
+      </c>
+      <c r="F98" s="17">
+        <f>'pengestrom_raw_10360641'!$F$2</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B99" s="17">
+        <f>'pengestrom_raw_10360641'!$B$3</f>
+        <v/>
+      </c>
+      <c r="C99" s="17">
+        <f>'pengestrom_raw_10360641'!$C$3</f>
+        <v/>
+      </c>
+      <c r="D99" s="17">
+        <f>'pengestrom_raw_10360641'!$D$3</f>
+        <v/>
+      </c>
+      <c r="E99" s="17">
+        <f>'pengestrom_raw_10360641'!$E$3</f>
+        <v/>
+      </c>
+      <c r="F99" s="17">
+        <f>'pengestrom_raw_10360641'!$F$3</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B100" s="17">
+        <f>'pengestrom_raw_10360641'!$B$4</f>
+        <v/>
+      </c>
+      <c r="C100" s="17">
+        <f>'pengestrom_raw_10360641'!$C$4</f>
+        <v/>
+      </c>
+      <c r="D100" s="17">
+        <f>'pengestrom_raw_10360641'!$D$4</f>
+        <v/>
+      </c>
+      <c r="E100" s="17">
+        <f>'pengestrom_raw_10360641'!$E$4</f>
+        <v/>
+      </c>
+      <c r="F100" s="17">
+        <f>'pengestrom_raw_10360641'!$F$4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm (rapporteret)</t>
+        </is>
+      </c>
+      <c r="B101" s="17">
+        <f>'pengestrom_raw_10360641'!$B$5</f>
+        <v/>
+      </c>
+      <c r="C101" s="17">
+        <f>'pengestrom_raw_10360641'!$C$5</f>
+        <v/>
+      </c>
+      <c r="D101" s="17">
+        <f>'pengestrom_raw_10360641'!$D$5</f>
+        <v/>
+      </c>
+      <c r="E101" s="17">
+        <f>'pengestrom_raw_10360641'!$E$5</f>
+        <v/>
+      </c>
+      <c r="F101" s="17">
+        <f>'pengestrom_raw_10360641'!$F$5</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="16" t="inlineStr">
+        <is>
+          <t>Krydstjek: drift + inv. + fin. = årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B102">
+        <f>IF(ABS(('pengestrom_raw_10360641'!$B$2+'pengestrom_raw_10360641'!$B$3+'pengestrom_raw_10360641'!$B$4)-'pengestrom_raw_10360641'!$B$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_10360641'!$B$2+'pengestrom_raw_10360641'!$B$3+'pengestrom_raw_10360641'!$B$4)-'pengestrom_raw_10360641'!$B$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="C102">
+        <f>IF(ABS(('pengestrom_raw_10360641'!$C$2+'pengestrom_raw_10360641'!$C$3+'pengestrom_raw_10360641'!$C$4)-'pengestrom_raw_10360641'!$C$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_10360641'!$C$2+'pengestrom_raw_10360641'!$C$3+'pengestrom_raw_10360641'!$C$4)-'pengestrom_raw_10360641'!$C$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="D102">
+        <f>IF(ABS(('pengestrom_raw_10360641'!$D$2+'pengestrom_raw_10360641'!$D$3+'pengestrom_raw_10360641'!$D$4)-'pengestrom_raw_10360641'!$D$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_10360641'!$D$2+'pengestrom_raw_10360641'!$D$3+'pengestrom_raw_10360641'!$D$4)-'pengestrom_raw_10360641'!$D$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="E102">
+        <f>IF(ABS(('pengestrom_raw_10360641'!$E$2+'pengestrom_raw_10360641'!$E$3+'pengestrom_raw_10360641'!$E$4)-'pengestrom_raw_10360641'!$E$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_10360641'!$E$2+'pengestrom_raw_10360641'!$E$3+'pengestrom_raw_10360641'!$E$4)-'pengestrom_raw_10360641'!$E$5,"+#,##0;-#,##0"))</f>
+        <v/>
+      </c>
+      <c r="F102">
+        <f>IF(ABS(('pengestrom_raw_10360641'!$F$2+'pengestrom_raw_10360641'!$F$3+'pengestrom_raw_10360641'!$F$4)-'pengestrom_raw_10360641'!$F$5)&lt;=2,"✓","⚠ "&amp;TEXT(('pengestrom_raw_10360641'!$F$2+'pengestrom_raw_10360641'!$F$3+'pengestrom_raw_10360641'!$F$4)-'pengestrom_raw_10360641'!$F$5,"+#,##0;-#,##0"))</f>
         <v/>
       </c>
     </row>
@@ -4625,402 +4801,402 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Nettoomsætning</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
-        <v>3777761</v>
-      </c>
-      <c r="C2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>3769844</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>3882492</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>3997019</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>4238726</v>
       </c>
+      <c r="F2" s="17" t="n">
+        <v>4390045</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Andre driftsindtægter</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n">
-        <v>1048</v>
-      </c>
-      <c r="C3" s="16" t="n">
+      <c r="B3" s="17" t="n">
         <v>12544</v>
       </c>
-      <c r="D3" s="16" t="n">
+      <c r="C3" s="17" t="n">
         <v>13485</v>
       </c>
-      <c r="E3" s="16" t="n">
+      <c r="D3" s="17" t="n">
         <v>22235</v>
       </c>
-      <c r="F3" s="16" t="n">
+      <c r="E3" s="17" t="n">
         <v>23697</v>
       </c>
+      <c r="F3" s="17" t="n">
+        <v>26896</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Vareforbrug</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>2473888</v>
-      </c>
-      <c r="C4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>2437420</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>2607385</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>2697074</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>2780119</v>
       </c>
+      <c r="F4" s="17" t="n">
+        <v>2862300</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Andre eksterne omkostninger</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>363067</v>
-      </c>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>368726</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>383479</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>403802</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>435600</v>
       </c>
+      <c r="F5" s="17" t="n">
+        <v>481060</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>Bruttoresultat</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n">
-        <v>941854</v>
-      </c>
-      <c r="C6" s="16" t="n">
+      <c r="B6" s="17" t="n">
         <v>976242</v>
       </c>
-      <c r="D6" s="16" t="n">
+      <c r="C6" s="17" t="n">
         <v>905113</v>
       </c>
-      <c r="E6" s="16" t="n">
+      <c r="D6" s="17" t="n">
         <v>918378</v>
       </c>
-      <c r="F6" s="16" t="n">
+      <c r="E6" s="17" t="n">
         <v>1046704</v>
       </c>
+      <c r="F6" s="17" t="n">
+        <v>1073581</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>Personaleomkostninger</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
-        <v>381825</v>
-      </c>
-      <c r="C7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>406171</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>404434</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>424123</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>457659</v>
       </c>
+      <c r="F7" s="17" t="n">
+        <v>499062</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Resultat før afskrivninger</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Af- og nedskrivninger</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>55744</v>
-      </c>
-      <c r="C9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>57288</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>57637</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>59652</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>59312</v>
       </c>
+      <c r="F9" s="17" t="n">
+        <v>59516</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Andre driftsomkostninger</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
-        <v>273</v>
-      </c>
-      <c r="C10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>412</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>1424</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>258</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>160</v>
       </c>
+      <c r="F10" s="17" t="n">
+        <v>1096</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Resultat af primær drift</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>504012</v>
-      </c>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>512371</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>441618</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>434345</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>529573</v>
       </c>
+      <c r="F11" s="17" t="n">
+        <v>513907</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Indtægter af kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n"/>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Finansielle indtægter</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n">
-        <v>8258</v>
-      </c>
-      <c r="C13" s="16" t="n">
+      <c r="B13" s="17" t="n">
         <v>14594</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="C13" s="17" t="n">
         <v>8851</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <v>58121</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <v>60830</v>
       </c>
+      <c r="F13" s="17" t="n">
+        <v>64567</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Finansielle omkostninger</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
-        <v>3576</v>
-      </c>
-      <c r="C14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>1873</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>36300</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>1207</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>2560</v>
       </c>
+      <c r="F14" s="17" t="n">
+        <v>1615</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Finansielle poster, netto</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n"/>
-      <c r="C15" s="16" t="n"/>
-      <c r="D15" s="16" t="n"/>
-      <c r="E15" s="16" t="n"/>
-      <c r="F15" s="16" t="n"/>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="17" t="n"/>
+      <c r="D15" s="17" t="n"/>
+      <c r="E15" s="17" t="n"/>
+      <c r="F15" s="17" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Resultat før skat</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
-        <v>508694</v>
-      </c>
-      <c r="C16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>525092</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>414169</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>491259</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>587843</v>
       </c>
+      <c r="F16" s="17" t="n">
+        <v>576859</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Skat af årets resultat</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
-        <v>112121</v>
-      </c>
-      <c r="C17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>115299</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>90701</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>107802</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>129503</v>
       </c>
+      <c r="F17" s="17" t="n">
+        <v>127002</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>Årets resultat</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
-        <v>396573</v>
-      </c>
-      <c r="C18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>409793</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>323468</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>383457</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>458340</v>
       </c>
+      <c r="F18" s="17" t="n">
+        <v>449857</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Gns. antal medarbejdere</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
-        <v>908</v>
-      </c>
-      <c r="C19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>931</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>958</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>925</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>954</v>
       </c>
+      <c r="F19" s="17" t="n">
+        <v>1005</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Investering i materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n">
-        <v>-56451</v>
-      </c>
-      <c r="C20" s="16" t="n">
+      <c r="B20" s="17" t="n">
         <v>-58277</v>
       </c>
-      <c r="D20" s="16" t="n">
+      <c r="C20" s="17" t="n">
         <v>-70026</v>
       </c>
-      <c r="E20" s="16" t="n">
+      <c r="D20" s="17" t="n">
         <v>-40377</v>
       </c>
-      <c r="F20" s="16" t="n">
+      <c r="E20" s="17" t="n">
         <v>-62424</v>
+      </c>
+      <c r="F20" s="17" t="n">
+        <v>-78004</v>
       </c>
     </row>
   </sheetData>
@@ -5052,995 +5228,997 @@
         </is>
       </c>
       <c r="B1" s="3" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="C1" s="3" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D1" s="3" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E1" s="3" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="F1" s="3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Grunde og bygninger</t>
         </is>
       </c>
-      <c r="B2" s="16" t="n">
-        <v>12414</v>
-      </c>
-      <c r="C2" s="16" t="n">
+      <c r="B2" s="17" t="n">
         <v>12269</v>
       </c>
-      <c r="D2" s="16" t="n">
+      <c r="C2" s="17" t="n">
         <v>12123</v>
       </c>
-      <c r="E2" s="16" t="n">
+      <c r="D2" s="17" t="n">
         <v>12127</v>
       </c>
-      <c r="F2" s="16" t="n">
+      <c r="E2" s="17" t="n">
         <v>11980</v>
       </c>
+      <c r="F2" s="17" t="n">
+        <v>11833</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="15" t="inlineStr">
+      <c r="A3" s="16" t="inlineStr">
         <is>
           <t>Produktionsanlæg og maskiner</t>
         </is>
       </c>
-      <c r="B3" s="16" t="n"/>
-      <c r="C3" s="16" t="n"/>
-      <c r="D3" s="16" t="n"/>
-      <c r="E3" s="16" t="n"/>
-      <c r="F3" s="16" t="n"/>
+      <c r="B3" s="17" t="n"/>
+      <c r="C3" s="17" t="n"/>
+      <c r="D3" s="17" t="n"/>
+      <c r="E3" s="17" t="n"/>
+      <c r="F3" s="17" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Driftsmateriel og inventar</t>
         </is>
       </c>
-      <c r="B4" s="16" t="n">
-        <v>114602</v>
-      </c>
-      <c r="C4" s="16" t="n">
+      <c r="B4" s="17" t="n">
         <v>106131</v>
       </c>
-      <c r="D4" s="16" t="n">
+      <c r="C4" s="17" t="n">
         <v>111531</v>
       </c>
-      <c r="E4" s="16" t="n">
+      <c r="D4" s="17" t="n">
         <v>100948</v>
       </c>
-      <c r="F4" s="16" t="n">
+      <c r="E4" s="17" t="n">
         <v>99962</v>
       </c>
+      <c r="F4" s="17" t="n">
+        <v>124539</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>Indretning af lejede lokaler</t>
         </is>
       </c>
-      <c r="B5" s="16" t="n">
-        <v>135621</v>
-      </c>
-      <c r="C5" s="16" t="n">
+      <c r="B5" s="17" t="n">
         <v>144795</v>
       </c>
-      <c r="D5" s="16" t="n">
+      <c r="C5" s="17" t="n">
         <v>149746</v>
       </c>
-      <c r="E5" s="16" t="n">
+      <c r="D5" s="17" t="n">
         <v>139060</v>
       </c>
-      <c r="F5" s="16" t="n">
+      <c r="E5" s="17" t="n">
         <v>141559</v>
       </c>
+      <c r="F5" s="17" t="n">
+        <v>134489</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>Forudbetaling og anlægsaktiver under opførelse</t>
         </is>
       </c>
-      <c r="B6" s="16" t="n"/>
-      <c r="C6" s="16" t="n"/>
-      <c r="D6" s="16" t="n"/>
-      <c r="E6" s="16" t="n"/>
-      <c r="F6" s="16" t="n">
+      <c r="B6" s="17" t="n"/>
+      <c r="C6" s="17" t="n"/>
+      <c r="D6" s="17" t="n"/>
+      <c r="E6" s="17" t="n">
         <v>1172</v>
       </c>
+      <c r="F6" s="17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>Materielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
-        <v>262637</v>
-      </c>
-      <c r="C7" s="16" t="n">
+      <c r="B7" s="17" t="n">
         <v>263195</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="C7" s="17" t="n">
         <v>273400</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="D7" s="17" t="n">
         <v>252135</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="E7" s="17" t="n">
         <v>254673</v>
       </c>
+      <c r="F7" s="17" t="n">
+        <v>270861</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Kapitalandele, dattervirksomheder</t>
         </is>
       </c>
-      <c r="B8" s="16" t="n"/>
-      <c r="C8" s="16" t="n"/>
-      <c r="D8" s="16" t="n"/>
-      <c r="E8" s="16" t="n"/>
-      <c r="F8" s="16" t="n"/>
+      <c r="B8" s="17" t="n"/>
+      <c r="C8" s="17" t="n"/>
+      <c r="D8" s="17" t="n"/>
+      <c r="E8" s="17" t="n"/>
+      <c r="F8" s="17" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Deposita</t>
         </is>
       </c>
-      <c r="B9" s="16" t="n">
-        <v>1317</v>
-      </c>
-      <c r="C9" s="16" t="n">
+      <c r="B9" s="17" t="n">
         <v>1345</v>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="C9" s="17" t="n">
         <v>990</v>
       </c>
-      <c r="E9" s="16" t="n">
+      <c r="D9" s="17" t="n">
         <v>1019</v>
       </c>
-      <c r="F9" s="16" t="n">
+      <c r="E9" s="17" t="n">
         <v>2038</v>
       </c>
+      <c r="F9" s="17" t="n">
+        <v>1970</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>Finansielle anlægsaktiver</t>
         </is>
       </c>
-      <c r="B10" s="16" t="n">
-        <v>1317</v>
-      </c>
-      <c r="C10" s="16" t="n">
+      <c r="B10" s="17" t="n">
         <v>1345</v>
       </c>
-      <c r="D10" s="16" t="n">
+      <c r="C10" s="17" t="n">
         <v>990</v>
       </c>
-      <c r="E10" s="16" t="n">
+      <c r="D10" s="17" t="n">
         <v>1019</v>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="E10" s="17" t="n">
         <v>2038</v>
       </c>
+      <c r="F10" s="17" t="n">
+        <v>1970</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Anlægsaktiver</t>
         </is>
       </c>
-      <c r="B11" s="16" t="n">
-        <v>263954</v>
-      </c>
-      <c r="C11" s="16" t="n">
+      <c r="B11" s="17" t="n">
         <v>264540</v>
       </c>
-      <c r="D11" s="16" t="n">
+      <c r="C11" s="17" t="n">
         <v>274390</v>
       </c>
-      <c r="E11" s="16" t="n">
+      <c r="D11" s="17" t="n">
         <v>253154</v>
       </c>
-      <c r="F11" s="16" t="n">
+      <c r="E11" s="17" t="n">
         <v>256711</v>
       </c>
+      <c r="F11" s="17" t="n">
+        <v>272831</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Råvarer og hjælpematerialer</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n"/>
+      <c r="B12" s="17" t="n"/>
+      <c r="C12" s="17" t="n"/>
+      <c r="D12" s="17" t="n"/>
+      <c r="E12" s="17" t="n"/>
+      <c r="F12" s="17" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
         <is>
           <t>Varer under fremstilling</t>
         </is>
       </c>
-      <c r="B13" s="16" t="n"/>
-      <c r="C13" s="16" t="n"/>
-      <c r="D13" s="16" t="n"/>
-      <c r="E13" s="16" t="n"/>
-      <c r="F13" s="16" t="n"/>
+      <c r="B13" s="17" t="n"/>
+      <c r="C13" s="17" t="n"/>
+      <c r="D13" s="17" t="n"/>
+      <c r="E13" s="17" t="n"/>
+      <c r="F13" s="17" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Færdigvarer og handelsvarer</t>
         </is>
       </c>
-      <c r="B14" s="16" t="n">
-        <v>396322</v>
-      </c>
-      <c r="C14" s="16" t="n">
+      <c r="B14" s="17" t="n">
         <v>449920</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="C14" s="17" t="n">
         <v>577693</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <v>505330</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <v>501146</v>
       </c>
+      <c r="F14" s="17" t="n">
+        <v>521956</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>Varebeholdninger</t>
         </is>
       </c>
-      <c r="B15" s="16" t="n">
-        <v>396322</v>
-      </c>
-      <c r="C15" s="16" t="n">
+      <c r="B15" s="17" t="n">
         <v>449920</v>
       </c>
-      <c r="D15" s="16" t="n">
+      <c r="C15" s="17" t="n">
         <v>577693</v>
       </c>
-      <c r="E15" s="16" t="n">
+      <c r="D15" s="17" t="n">
         <v>505330</v>
       </c>
-      <c r="F15" s="16" t="n">
+      <c r="E15" s="17" t="n">
         <v>501146</v>
       </c>
+      <c r="F15" s="17" t="n">
+        <v>521956</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender fra salg og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B16" s="16" t="n">
-        <v>1470</v>
-      </c>
-      <c r="C16" s="16" t="n">
+      <c r="B16" s="17" t="n">
         <v>1707</v>
       </c>
-      <c r="D16" s="16" t="n">
+      <c r="C16" s="17" t="n">
         <v>3794</v>
       </c>
-      <c r="E16" s="16" t="n">
+      <c r="D16" s="17" t="n">
         <v>13732</v>
       </c>
-      <c r="F16" s="16" t="n">
+      <c r="E16" s="17" t="n">
         <v>15</v>
       </c>
+      <c r="F16" s="17" t="n">
+        <v>1094</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavender hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B17" s="16" t="n">
-        <v>74008</v>
-      </c>
-      <c r="C17" s="16" t="n">
+      <c r="B17" s="17" t="n">
         <v>64694</v>
       </c>
-      <c r="D17" s="16" t="n">
+      <c r="C17" s="17" t="n">
         <v>363603</v>
       </c>
-      <c r="E17" s="16" t="n">
+      <c r="D17" s="17" t="n">
         <v>405298</v>
       </c>
-      <c r="F17" s="16" t="n">
+      <c r="E17" s="17" t="n">
         <v>338201</v>
       </c>
+      <c r="F17" s="17" t="n">
+        <v>780112</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Andre tilgodehavender</t>
         </is>
       </c>
-      <c r="B18" s="16" t="n">
-        <v>299653</v>
-      </c>
-      <c r="C18" s="16" t="n">
+      <c r="B18" s="17" t="n">
         <v>536335</v>
       </c>
-      <c r="D18" s="16" t="n">
+      <c r="C18" s="17" t="n">
         <v>31907</v>
       </c>
-      <c r="E18" s="16" t="n">
+      <c r="D18" s="17" t="n">
         <v>29931</v>
       </c>
-      <c r="F18" s="16" t="n">
+      <c r="E18" s="17" t="n">
         <v>86765</v>
       </c>
+      <c r="F18" s="17" t="n">
+        <v>62478</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (aktiver)</t>
         </is>
       </c>
-      <c r="B19" s="16" t="n">
-        <v>15805</v>
-      </c>
-      <c r="C19" s="16" t="n">
+      <c r="B19" s="17" t="n">
         <v>18447</v>
       </c>
-      <c r="D19" s="16" t="n">
+      <c r="C19" s="17" t="n">
         <v>17771</v>
       </c>
-      <c r="E19" s="16" t="n">
+      <c r="D19" s="17" t="n">
         <v>20931</v>
       </c>
-      <c r="F19" s="16" t="n">
+      <c r="E19" s="17" t="n">
         <v>17468</v>
       </c>
+      <c r="F19" s="17" t="n">
+        <v>19168</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Udskudt skatteaktiv</t>
         </is>
       </c>
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="n"/>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="n"/>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+      <c r="A21" s="16" t="inlineStr">
         <is>
           <t>Tilgodehavende skat hos tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B21" s="16" t="n"/>
-      <c r="C21" s="16" t="n"/>
-      <c r="D21" s="16" t="n"/>
-      <c r="E21" s="16" t="n"/>
-      <c r="F21" s="16" t="n"/>
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="n"/>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="inlineStr">
+      <c r="A22" s="16" t="inlineStr">
         <is>
           <t>Kortfristede skattetilgodehavender</t>
         </is>
       </c>
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="16" t="n"/>
-      <c r="E22" s="16" t="n"/>
-      <c r="F22" s="16" t="n"/>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>Tilgodehavender</t>
         </is>
       </c>
-      <c r="B23" s="16" t="n">
-        <v>390936</v>
-      </c>
-      <c r="C23" s="16" t="n">
+      <c r="B23" s="17" t="n">
         <v>621183</v>
       </c>
-      <c r="D23" s="16" t="n">
+      <c r="C23" s="17" t="n">
         <v>417075</v>
       </c>
-      <c r="E23" s="16" t="n">
+      <c r="D23" s="17" t="n">
         <v>469892</v>
       </c>
-      <c r="F23" s="16" t="n">
+      <c r="E23" s="17" t="n">
         <v>442449</v>
       </c>
+      <c r="F23" s="17" t="n">
+        <v>862852</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="inlineStr">
+      <c r="A24" s="16" t="inlineStr">
         <is>
           <t>Værdipapirer</t>
         </is>
       </c>
-      <c r="B24" s="16" t="n">
-        <v>211617</v>
-      </c>
-      <c r="C24" s="16" t="n">
+      <c r="B24" s="17" t="n">
         <v>225312</v>
       </c>
-      <c r="D24" s="16" t="n">
+      <c r="C24" s="17" t="n">
         <v>129879</v>
       </c>
-      <c r="E24" s="16" t="n">
+      <c r="D24" s="17" t="n">
         <v>625704</v>
       </c>
-      <c r="F24" s="16" t="n">
+      <c r="E24" s="17" t="n">
         <v>825582</v>
       </c>
+      <c r="F24" s="17" t="n">
+        <v>891899</v>
+      </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Likvide beholdninger</t>
         </is>
       </c>
-      <c r="B25" s="16" t="n">
-        <v>80481</v>
-      </c>
-      <c r="C25" s="16" t="n">
+      <c r="B25" s="17" t="n">
         <v>74833</v>
       </c>
-      <c r="D25" s="16" t="n">
+      <c r="C25" s="17" t="n">
         <v>220644</v>
       </c>
-      <c r="E25" s="16" t="n">
+      <c r="D25" s="17" t="n">
         <v>177212</v>
       </c>
-      <c r="F25" s="16" t="n">
+      <c r="E25" s="17" t="n">
         <v>297642</v>
       </c>
+      <c r="F25" s="17" t="n">
+        <v>218420</v>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>Omsætningsaktiver</t>
         </is>
       </c>
-      <c r="B26" s="16" t="n">
-        <v>1079356</v>
-      </c>
-      <c r="C26" s="16" t="n">
+      <c r="B26" s="17" t="n">
         <v>1371248</v>
       </c>
-      <c r="D26" s="16" t="n">
+      <c r="C26" s="17" t="n">
         <v>1345291</v>
       </c>
-      <c r="E26" s="16" t="n">
+      <c r="D26" s="17" t="n">
         <v>1778138</v>
       </c>
-      <c r="F26" s="16" t="n">
+      <c r="E26" s="17" t="n">
         <v>2066819</v>
       </c>
+      <c r="F26" s="17" t="n">
+        <v>2495127</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>Aktiver</t>
         </is>
       </c>
-      <c r="B27" s="16" t="n">
-        <v>1343310</v>
-      </c>
-      <c r="C27" s="16" t="n">
+      <c r="B27" s="17" t="n">
         <v>1635788</v>
       </c>
-      <c r="D27" s="16" t="n">
+      <c r="C27" s="17" t="n">
         <v>1619681</v>
       </c>
-      <c r="E27" s="16" t="n">
+      <c r="D27" s="17" t="n">
         <v>2031292</v>
       </c>
-      <c r="F27" s="16" t="n">
+      <c r="E27" s="17" t="n">
         <v>2323530</v>
       </c>
+      <c r="F27" s="17" t="n">
+        <v>2767958</v>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Selskabskapital</t>
         </is>
       </c>
-      <c r="B28" s="16" t="n">
+      <c r="B28" s="17" t="n">
         <v>3000</v>
       </c>
-      <c r="C28" s="16" t="n">
+      <c r="C28" s="17" t="n">
         <v>3000</v>
       </c>
-      <c r="D28" s="16" t="n">
+      <c r="D28" s="17" t="n">
         <v>3000</v>
       </c>
-      <c r="E28" s="16" t="n">
+      <c r="E28" s="17" t="n">
         <v>3000</v>
       </c>
-      <c r="F28" s="16" t="n">
+      <c r="F28" s="17" t="n">
         <v>3000</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
+      <c r="A29" s="16" t="inlineStr">
         <is>
           <t>Reserve for nettoopskrivning (indre værdis metode)</t>
         </is>
       </c>
-      <c r="B29" s="16" t="n"/>
-      <c r="C29" s="16" t="n"/>
-      <c r="D29" s="16" t="n"/>
-      <c r="E29" s="16" t="n"/>
-      <c r="F29" s="16" t="n"/>
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="n"/>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="17" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="16" t="inlineStr">
         <is>
           <t>Reserve for udviklingsomkostninger</t>
         </is>
       </c>
-      <c r="B30" s="16" t="n"/>
-      <c r="C30" s="16" t="n"/>
-      <c r="D30" s="16" t="n"/>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="16" t="n"/>
+      <c r="B30" s="17" t="n"/>
+      <c r="C30" s="17" t="n"/>
+      <c r="D30" s="17" t="n"/>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="17" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Reserve for sikringstransaktioner</t>
         </is>
       </c>
-      <c r="B31" s="16" t="n"/>
-      <c r="C31" s="16" t="n"/>
-      <c r="D31" s="16" t="n"/>
-      <c r="E31" s="16" t="n">
+      <c r="B31" s="17" t="n"/>
+      <c r="C31" s="17" t="n"/>
+      <c r="D31" s="17" t="n">
         <v>1530</v>
       </c>
-      <c r="F31" s="16" t="n">
+      <c r="E31" s="17" t="n">
         <v>1592</v>
       </c>
+      <c r="F31" s="17" t="n">
+        <v>1673</v>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="inlineStr">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>Andre reserver</t>
         </is>
       </c>
-      <c r="B32" s="16" t="n"/>
-      <c r="C32" s="16" t="n"/>
-      <c r="D32" s="16" t="n"/>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="16" t="n"/>
+      <c r="B32" s="17" t="n"/>
+      <c r="C32" s="17" t="n"/>
+      <c r="D32" s="17" t="n"/>
+      <c r="E32" s="17" t="n"/>
+      <c r="F32" s="17" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="inlineStr">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>Overført resultat</t>
         </is>
       </c>
-      <c r="B33" s="16" t="n">
-        <v>865379</v>
-      </c>
-      <c r="C33" s="16" t="n">
+      <c r="B33" s="17" t="n">
         <v>1275172</v>
       </c>
-      <c r="D33" s="16" t="n">
+      <c r="C33" s="17" t="n">
         <v>1273641</v>
       </c>
-      <c r="E33" s="16" t="n">
+      <c r="D33" s="17" t="n">
         <v>1493954</v>
       </c>
-      <c r="F33" s="16" t="n">
+      <c r="E33" s="17" t="n">
         <v>1952295</v>
       </c>
+      <c r="F33" s="17" t="n">
+        <v>2112152</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>Egenkapital i alt</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n">
-        <v>942381</v>
-      </c>
-      <c r="C34" s="16" t="n">
+      <c r="B34" s="17" t="n">
         <v>1278660</v>
       </c>
-      <c r="D34" s="16" t="n">
+      <c r="C34" s="17" t="n">
         <v>1278293</v>
       </c>
-      <c r="E34" s="16" t="n">
+      <c r="D34" s="17" t="n">
         <v>1661624</v>
       </c>
-      <c r="F34" s="16" t="n">
+      <c r="E34" s="17" t="n">
         <v>1956887</v>
       </c>
+      <c r="F34" s="17" t="n">
+        <v>2406825</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="15" t="inlineStr">
+      <c r="A35" s="16" t="inlineStr">
         <is>
           <t>Hensættelse til udskudt skat</t>
         </is>
       </c>
-      <c r="B35" s="16" t="n">
-        <v>3200</v>
-      </c>
-      <c r="C35" s="16" t="n">
+      <c r="B35" s="17" t="n">
         <v>3008</v>
       </c>
-      <c r="D35" s="16" t="n">
+      <c r="C35" s="17" t="n">
         <v>3593</v>
       </c>
-      <c r="E35" s="16" t="n">
+      <c r="D35" s="17" t="n">
         <v>3827</v>
       </c>
-      <c r="F35" s="16" t="n">
+      <c r="E35" s="17" t="n">
         <v>3977</v>
       </c>
+      <c r="F35" s="17" t="n">
+        <v>5605</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>Hensatte forpligtelser</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n">
-        <v>4873</v>
-      </c>
-      <c r="C36" s="16" t="n">
+      <c r="B36" s="17" t="n">
         <v>4398</v>
       </c>
-      <c r="D36" s="16" t="n">
+      <c r="C36" s="17" t="n">
         <v>4912</v>
       </c>
-      <c r="E36" s="16" t="n">
+      <c r="D36" s="17" t="n">
         <v>5223</v>
       </c>
-      <c r="F36" s="16" t="n">
+      <c r="E36" s="17" t="n">
         <v>5398</v>
       </c>
+      <c r="F36" s="17" t="n">
+        <v>7003</v>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (langfristet)</t>
         </is>
       </c>
-      <c r="B37" s="16" t="n"/>
-      <c r="C37" s="16" t="n"/>
-      <c r="D37" s="16" t="n"/>
-      <c r="E37" s="16" t="n"/>
-      <c r="F37" s="16" t="n"/>
+      <c r="B37" s="17" t="n"/>
+      <c r="C37" s="17" t="n"/>
+      <c r="D37" s="17" t="n"/>
+      <c r="E37" s="17" t="n"/>
+      <c r="F37" s="17" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="15" t="inlineStr">
+      <c r="A38" s="16" t="inlineStr">
         <is>
           <t>Langfristede lån</t>
         </is>
       </c>
-      <c r="B38" s="16" t="n">
-        <v>5648</v>
-      </c>
-      <c r="C38" s="16" t="n">
+      <c r="B38" s="17" t="n">
         <v>5251</v>
       </c>
-      <c r="D38" s="16" t="n">
+      <c r="C38" s="17" t="n">
         <v>4863</v>
       </c>
-      <c r="E38" s="16" t="n">
+      <c r="D38" s="17" t="n">
         <v>4652</v>
       </c>
-      <c r="F38" s="16" t="n">
+      <c r="E38" s="17" t="n">
         <v>4329</v>
       </c>
+      <c r="F38" s="17" t="n">
+        <v>3935</v>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="15" t="inlineStr">
+      <c r="A39" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (langfristet)</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n"/>
-      <c r="C39" s="16" t="n"/>
-      <c r="D39" s="16" t="n"/>
-      <c r="E39" s="16" t="n"/>
-      <c r="F39" s="16" t="n"/>
+      <c r="B39" s="17" t="n"/>
+      <c r="C39" s="17" t="n"/>
+      <c r="D39" s="17" t="n"/>
+      <c r="E39" s="17" t="n"/>
+      <c r="F39" s="17" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="15" t="inlineStr">
+      <c r="A40" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (langfristet)</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n">
-        <v>29620</v>
-      </c>
-      <c r="C40" s="16" t="n">
+      <c r="B40" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="D40" s="16" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="16" t="n"/>
+      <c r="C40" s="17" t="n"/>
+      <c r="D40" s="17" t="n"/>
+      <c r="E40" s="17" t="n"/>
+      <c r="F40" s="17" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="17" t="inlineStr">
+      <c r="A41" s="15" t="inlineStr">
         <is>
           <t>Langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B41" s="16" t="n">
-        <v>35268</v>
-      </c>
-      <c r="C41" s="16" t="n">
+      <c r="B41" s="17" t="n">
         <v>5251</v>
       </c>
-      <c r="D41" s="16" t="n">
+      <c r="C41" s="17" t="n">
         <v>4863</v>
       </c>
-      <c r="E41" s="16" t="n">
+      <c r="D41" s="17" t="n">
         <v>4652</v>
       </c>
-      <c r="F41" s="16" t="n">
+      <c r="E41" s="17" t="n">
         <v>4329</v>
       </c>
+      <c r="F41" s="17" t="n">
+        <v>3935</v>
+      </c>
     </row>
     <row r="42">
-      <c r="A42" s="15" t="inlineStr">
+      <c r="A42" s="16" t="inlineStr">
         <is>
           <t>Ansvarlig lånekapital (kortfristet)</t>
         </is>
       </c>
-      <c r="B42" s="16" t="n"/>
-      <c r="C42" s="16" t="n"/>
-      <c r="D42" s="16" t="n"/>
-      <c r="E42" s="16" t="n"/>
-      <c r="F42" s="16" t="n"/>
+      <c r="B42" s="17" t="n"/>
+      <c r="C42" s="17" t="n"/>
+      <c r="D42" s="17" t="n"/>
+      <c r="E42" s="17" t="n"/>
+      <c r="F42" s="17" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="15" t="inlineStr">
+      <c r="A43" s="16" t="inlineStr">
         <is>
           <t>Kortfristet del af langfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B43" s="16" t="n"/>
-      <c r="C43" s="16" t="n"/>
-      <c r="D43" s="16" t="n"/>
-      <c r="E43" s="16" t="n"/>
-      <c r="F43" s="16" t="n"/>
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="17" t="n"/>
+      <c r="D43" s="17" t="n"/>
+      <c r="E43" s="17" t="n"/>
+      <c r="F43" s="17" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="15" t="inlineStr">
+      <c r="A44" s="16" t="inlineStr">
         <is>
           <t>Kreditinstitutter</t>
         </is>
       </c>
-      <c r="B44" s="16" t="n">
-        <v>81</v>
-      </c>
-      <c r="C44" s="16" t="n">
+      <c r="B44" s="17" t="n">
         <v>575</v>
       </c>
-      <c r="D44" s="16" t="n">
+      <c r="C44" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="E44" s="16" t="n">
+      <c r="D44" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F44" s="16" t="n">
+      <c r="E44" s="17" t="n">
         <v>313</v>
       </c>
+      <c r="F44" s="17" t="n">
+        <v>355</v>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="15" t="inlineStr">
+      <c r="A45" s="16" t="inlineStr">
         <is>
           <t>Leasingforpligtelser (kortfristet)</t>
         </is>
       </c>
-      <c r="B45" s="16" t="n"/>
-      <c r="C45" s="16" t="n"/>
-      <c r="D45" s="16" t="n"/>
-      <c r="E45" s="16" t="n"/>
-      <c r="F45" s="16" t="n"/>
+      <c r="B45" s="17" t="n"/>
+      <c r="C45" s="17" t="n"/>
+      <c r="D45" s="17" t="n"/>
+      <c r="E45" s="17" t="n"/>
+      <c r="F45" s="17" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
+      <c r="A46" s="16" t="inlineStr">
         <is>
           <t>Leverandører af varer og tjenesteydelser</t>
         </is>
       </c>
-      <c r="B46" s="16" t="n">
-        <v>225411</v>
-      </c>
-      <c r="C46" s="16" t="n">
+      <c r="B46" s="17" t="n">
         <v>220723</v>
       </c>
-      <c r="D46" s="16" t="n">
+      <c r="C46" s="17" t="n">
         <v>227162</v>
       </c>
-      <c r="E46" s="16" t="n">
+      <c r="D46" s="17" t="n">
         <v>170880</v>
       </c>
-      <c r="F46" s="16" t="n">
+      <c r="E46" s="17" t="n">
         <v>197405</v>
       </c>
+      <c r="F46" s="17" t="n">
+        <v>177357</v>
+      </c>
     </row>
     <row r="47">
-      <c r="A47" s="15" t="inlineStr">
+      <c r="A47" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder</t>
         </is>
       </c>
-      <c r="B47" s="16" t="n"/>
-      <c r="C47" s="16" t="n"/>
-      <c r="D47" s="16" t="n"/>
-      <c r="E47" s="16" t="n">
+      <c r="B47" s="17" t="n"/>
+      <c r="C47" s="17" t="n"/>
+      <c r="D47" s="17" t="n">
         <v>51240</v>
       </c>
-      <c r="F47" s="16" t="n">
+      <c r="E47" s="17" t="n">
         <v>49476</v>
       </c>
+      <c r="F47" s="17" t="n">
+        <v>57258</v>
+      </c>
     </row>
     <row r="48">
-      <c r="A48" s="15" t="inlineStr">
+      <c r="A48" s="16" t="inlineStr">
         <is>
           <t>Gæld til selskabsdeltagere og ledelse</t>
         </is>
       </c>
-      <c r="B48" s="16" t="n"/>
-      <c r="C48" s="16" t="n"/>
-      <c r="D48" s="16" t="n"/>
-      <c r="E48" s="16" t="n"/>
-      <c r="F48" s="16" t="n"/>
+      <c r="B48" s="17" t="n"/>
+      <c r="C48" s="17" t="n"/>
+      <c r="D48" s="17" t="n"/>
+      <c r="E48" s="17" t="n"/>
+      <c r="F48" s="17" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="15" t="inlineStr">
+      <c r="A49" s="16" t="inlineStr">
         <is>
           <t>Selskabsskat</t>
         </is>
       </c>
-      <c r="B49" s="16" t="n">
-        <v>10044</v>
-      </c>
-      <c r="C49" s="16" t="n">
+      <c r="B49" s="17" t="n">
         <v>3783</v>
       </c>
-      <c r="D49" s="16" t="n">
+      <c r="C49" s="17" t="n">
         <v>3011</v>
       </c>
-      <c r="E49" s="16" t="n">
+      <c r="D49" s="17" t="n">
         <v>23614</v>
       </c>
-      <c r="F49" s="16" t="n">
+      <c r="E49" s="17" t="n">
         <v>7071</v>
       </c>
+      <c r="F49" s="17" t="n">
+        <v>11621</v>
+      </c>
     </row>
     <row r="50">
-      <c r="A50" s="15" t="inlineStr">
+      <c r="A50" s="16" t="inlineStr">
         <is>
           <t>Gæld til tilknyttede virksomheder vedr. selskabsskat</t>
         </is>
       </c>
-      <c r="B50" s="16" t="n"/>
-      <c r="C50" s="16" t="n"/>
-      <c r="D50" s="16" t="n"/>
-      <c r="E50" s="16" t="n"/>
-      <c r="F50" s="16" t="n"/>
+      <c r="B50" s="17" t="n"/>
+      <c r="C50" s="17" t="n"/>
+      <c r="D50" s="17" t="n"/>
+      <c r="E50" s="17" t="n"/>
+      <c r="F50" s="17" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="15" t="inlineStr">
+      <c r="A51" s="16" t="inlineStr">
         <is>
           <t>Anden gæld (kortfristet)</t>
         </is>
       </c>
-      <c r="B51" s="16" t="n">
-        <v>124852</v>
-      </c>
-      <c r="C51" s="16" t="n">
+      <c r="B51" s="17" t="n">
         <v>121998</v>
       </c>
-      <c r="D51" s="16" t="n"/>
-      <c r="E51" s="16" t="n"/>
-      <c r="F51" s="16" t="n"/>
+      <c r="C51" s="17" t="n"/>
+      <c r="D51" s="17" t="n"/>
+      <c r="E51" s="17" t="n"/>
+      <c r="F51" s="17" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="15" t="inlineStr">
+      <c r="A52" s="16" t="inlineStr">
         <is>
           <t>Periodeafgrænsningsposter (passiver)</t>
         </is>
       </c>
-      <c r="B52" s="16" t="n"/>
-      <c r="C52" s="16" t="n"/>
-      <c r="D52" s="16" t="n"/>
-      <c r="E52" s="16" t="n"/>
-      <c r="F52" s="16" t="n"/>
+      <c r="B52" s="17" t="n"/>
+      <c r="C52" s="17" t="n"/>
+      <c r="D52" s="17" t="n"/>
+      <c r="E52" s="17" t="n"/>
+      <c r="F52" s="17" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="17" t="inlineStr">
+      <c r="A53" s="15" t="inlineStr">
         <is>
           <t>Kortfristede gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B53" s="16" t="n">
-        <v>360788</v>
-      </c>
-      <c r="C53" s="16" t="n">
+      <c r="B53" s="17" t="n">
         <v>347479</v>
       </c>
-      <c r="D53" s="16" t="n">
+      <c r="C53" s="17" t="n">
         <v>331613</v>
       </c>
-      <c r="E53" s="16" t="n">
+      <c r="D53" s="17" t="n">
         <v>359793</v>
       </c>
-      <c r="F53" s="16" t="n">
+      <c r="E53" s="17" t="n">
         <v>356916</v>
       </c>
+      <c r="F53" s="17" t="n">
+        <v>350195</v>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="17" t="inlineStr">
+      <c r="A54" s="15" t="inlineStr">
         <is>
           <t>Gældsforpligtelser</t>
         </is>
       </c>
-      <c r="B54" s="16" t="n">
-        <v>396056</v>
-      </c>
-      <c r="C54" s="16" t="n">
+      <c r="B54" s="17" t="n">
         <v>352730</v>
       </c>
-      <c r="D54" s="16" t="n">
+      <c r="C54" s="17" t="n">
         <v>336476</v>
       </c>
-      <c r="E54" s="16" t="n">
+      <c r="D54" s="17" t="n">
         <v>364445</v>
       </c>
-      <c r="F54" s="16" t="n">
+      <c r="E54" s="17" t="n">
         <v>361245</v>
       </c>
+      <c r="F54" s="17" t="n">
+        <v>354130</v>
+      </c>
     </row>
     <row r="55">
-      <c r="A55" s="17" t="inlineStr">
+      <c r="A55" s="15" t="inlineStr">
         <is>
           <t>Passiver</t>
         </is>
       </c>
-      <c r="B55" s="16" t="n">
-        <v>1343310</v>
-      </c>
-      <c r="C55" s="16" t="n">
+      <c r="B55" s="17" t="n">
         <v>1635788</v>
       </c>
-      <c r="D55" s="16" t="n">
+      <c r="C55" s="17" t="n">
         <v>1619681</v>
       </c>
-      <c r="E55" s="16" t="n">
+      <c r="D55" s="17" t="n">
         <v>2031292</v>
       </c>
-      <c r="F55" s="16" t="n">
+      <c r="E55" s="17" t="n">
         <v>2323530</v>
+      </c>
+      <c r="F55" s="17" t="n">
+        <v>2767958</v>
       </c>
     </row>
   </sheetData>
@@ -6049,6 +6227,128 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Pengestrømsopgørelse (t.kr.)</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C1" s="3" t="n">
+        <v>2022</v>
+      </c>
+      <c r="D1" s="3" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E1" s="3" t="n">
+        <v>2024</v>
+      </c>
+      <c r="F1" s="3" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra driftsaktivitet</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="n">
+        <v>350742</v>
+      </c>
+      <c r="C2" s="17" t="n">
+        <v>271984</v>
+      </c>
+      <c r="D2" s="17" t="n">
+        <v>448173</v>
+      </c>
+      <c r="E2" s="17" t="n">
+        <v>489456</v>
+      </c>
+      <c r="F2" s="17" t="n">
+        <v>468169</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra investeringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>-51055</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>-306650</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>-491288</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>-163935</v>
+      </c>
+      <c r="F3" s="17" t="n">
+        <v>-105128</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="16" t="inlineStr">
+        <is>
+          <t>Pengestrømme fra finansieringsaktivitet</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
+        <v>-73903</v>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>-325956</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>-317</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>-163450</v>
+      </c>
+      <c r="F4" s="17" t="n">
+        <v>-442263</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Årets pengestrøm</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n"/>
+      <c r="C5" s="17" t="n"/>
+      <c r="D5" s="17" t="n"/>
+      <c r="E5" s="17" t="n"/>
+      <c r="F5" s="17" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6079,13 +6379,13 @@
         </is>
       </c>
       <c r="B3" s="20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C3" s="20" t="n">
         <v>2024</v>
       </c>
-      <c r="C3" s="20" t="n">
+      <c r="D3" s="20" t="n">
         <v>2023</v>
-      </c>
-      <c r="D3" s="20" t="n">
-        <v>2022</v>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
@@ -6799,7 +7099,7 @@
     <row r="40">
       <c r="A40" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for indtjeningsevne (2022=100)</t>
+          <t>Indekstal for indtjeningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B40" s="22" t="n"/>
@@ -6917,7 +7217,7 @@
     <row r="47">
       <c r="A47" s="22" t="inlineStr">
         <is>
-          <t>Indekstal for kapitaltilpasningsevne (2022=100)</t>
+          <t>Indekstal for kapitaltilpasningsevne (2023=100)</t>
         </is>
       </c>
       <c r="B47" s="22" t="n"/>
@@ -7093,7 +7393,7 @@
     <row r="58">
       <c r="A58" s="32" t="inlineStr">
         <is>
-          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2022-2024. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
+          <t>Kilde: Bearbejdet uddrag af årsrapporter for 2023-2025. Alle dataceller er live formler der peger på res_raw / balance_raw.</t>
         </is>
       </c>
       <c r="B58" s="29" t="n"/>
@@ -7269,4 +7569,141 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="38" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="62" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="33" t="inlineStr">
+        <is>
+          <t>Ukendte XBRL-felter — disse er noter og ikke en del af hoved-regnskabet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Kategori</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Dansk navn</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>XBRL feltnavn</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2021 t.kr.</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2022 t.kr.</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023 t.kr.</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2024 t.kr.</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2025 t.kr.</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>Forklaring</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="34" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B3" s="34" t="inlineStr">
+        <is>
+          <t>fsa:OtherContingentLiabilitiesNotRecognisedInBalanceSheetRelatedToGroupEnterprises</t>
+        </is>
+      </c>
+      <c r="C3" s="34" t="inlineStr">
+        <is>
+          <t>fsa:OtherContingentLiabilitiesNotRecognisedInBalanceSheetRelatedToGroupEnterprises</t>
+        </is>
+      </c>
+      <c r="D3" s="35" t="n"/>
+      <c r="E3" s="35" t="n"/>
+      <c r="F3" s="35" t="n"/>
+      <c r="G3" s="35" t="n"/>
+      <c r="H3" s="35" t="n">
+        <v>298297</v>
+      </c>
+      <c r="I3" s="36" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="37" t="inlineStr">
+        <is>
+          <t>Øvrige (ukendt)</t>
+        </is>
+      </c>
+      <c r="B4" s="37" t="inlineStr">
+        <is>
+          <t>fsa:RecourseAndNonrecourseGuaranteeCommitments</t>
+        </is>
+      </c>
+      <c r="C4" s="37" t="inlineStr">
+        <is>
+          <t>fsa:RecourseAndNonrecourseGuaranteeCommitments</t>
+        </is>
+      </c>
+      <c r="D4" s="38" t="n"/>
+      <c r="E4" s="38" t="n"/>
+      <c r="F4" s="38" t="n"/>
+      <c r="G4" s="38" t="n"/>
+      <c r="H4" s="38" t="n">
+        <v>43183</v>
+      </c>
+      <c r="I4" s="39" t="inlineStr">
+        <is>
+          <t>Ingen forklaring tilgængelig.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>